--- a/data/2026/forex_rates_2026-03-31.xlsx
+++ b/data/2026/forex_rates_2026-03-31.xlsx
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>93.73999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>93.73999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>93.84</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>93.95</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
